--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\minigame\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0739D93B-339F-4503-8C9D-35B2959C2383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1E645B-479E-4DE4-8130-AAA210BA9A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21920" yWindow="1680" windowWidth="15920" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameCharacters" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>ObjectID</t>
   </si>
@@ -67,6 +67,26 @@
   </si>
   <si>
     <t>CC_Bullet_1</t>
+  </si>
+  <si>
+    <t>番茄</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄炒蛋</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dish</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingredient</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1018,10 +1038,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1038,7 +1062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1055,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1072,7 +1096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1087,6 +1111,57 @@
       </c>
       <c r="E4">
         <v>8001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>201</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\minigame\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1E645B-479E-4DE4-8130-AAA210BA9A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-21920" yWindow="1680" windowWidth="15920" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="GameCharacters" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>ObjectID</t>
   </si>
@@ -42,18 +44,18 @@
     <t>InitModifier</t>
   </si>
   <si>
+    <t>基础敌人</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>CC_Enemy_01</t>
+  </si>
+  <si>
     <t>基础防御塔</t>
   </si>
   <si>
-    <t>CC_Enemy_01</t>
-  </si>
-  <si>
-    <t>基础敌人</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
     <t>Tower</t>
   </si>
   <si>
@@ -70,35 +72,41 @@
   </si>
   <si>
     <t>番茄</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dish</t>
+  </si>
+  <si>
+    <t>GO_Dish_Potato</t>
   </si>
   <si>
     <t>鸡蛋</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Dish_Egg</t>
   </si>
   <si>
     <t>番茄炒蛋</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dish</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingredient</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Dish_PotatoChaoEgg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -106,7 +114,29 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -114,16 +144,22 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -132,7 +168,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -141,7 +176,52 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -149,7 +229,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -157,7 +236,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -165,91 +243,13 @@
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -263,175 +263,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -441,6 +454,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -466,7 +494,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,15 +529,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -525,17 +544,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -551,131 +564,152 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -684,58 +718,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -784,7 +821,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -817,26 +854,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -869,23 +889,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1027,25 +1030,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="15.375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1062,29 +1060,29 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -1096,7 +1094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1113,7 +1111,7 @@
         <v>8001</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>101</v>
       </c>
@@ -1121,52 +1119,52 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>102</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>201</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>ObjectID</t>
   </si>
@@ -86,10 +86,22 @@
     <t>GO_Dish_Egg</t>
   </si>
   <si>
+    <t>炒番茄</t>
+  </si>
+  <si>
+    <t>GO_Dish_Dish1</t>
+  </si>
+  <si>
+    <t>炒鸡蛋</t>
+  </si>
+  <si>
+    <t>GO_Dish_Dish2</t>
+  </si>
+  <si>
     <t>番茄炒蛋</t>
   </si>
   <si>
-    <t>GO_Dish_PotatoChaoEgg</t>
+    <t>GO_Dish_Dish3</t>
   </si>
 </sst>
 </file>
@@ -102,14 +114,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,79 +573,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -652,7 +657,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -664,7 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -676,7 +681,7 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -688,7 +693,7 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -700,7 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -713,10 +718,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1036,11 +1045,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="4" max="4" width="33.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1112,10 +1121,10 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>101</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
@@ -1129,10 +1138,10 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>102</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
@@ -1146,10 +1155,10 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>201</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
@@ -1159,6 +1168,40 @@
         <v>20</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
+        <v>202</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
+        <v>203</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>ObjectID</t>
   </si>
@@ -69,6 +69,15 @@
   </si>
   <si>
     <t>CC_Bullet_1</t>
+  </si>
+  <si>
+    <t>空Character作为SpawenRoot</t>
+  </si>
+  <si>
+    <t>SpawnRoot</t>
+  </si>
+  <si>
+    <t>GO_SpawnRoot_1</t>
   </si>
   <si>
     <t>番茄</t>
@@ -1045,7 +1054,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="15.375" customWidth="1"/>
@@ -1121,10 +1130,10 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1">
-        <v>101</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
@@ -1139,16 +1148,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1156,16 +1165,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1173,16 +1182,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1190,18 +1199,35 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
+        <v>202</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
         <v>203</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9">
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unity\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2BDF78-F4FA-44DD-9B92-8310F848804E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF30D39-0C0D-474D-9CA0-C20762EAD487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="10600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameCharacters" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>ObjectID</t>
   </si>
@@ -110,13 +110,71 @@
   </si>
   <si>
     <t>CC_Enemy_03</t>
+  </si>
+  <si>
+    <t>GO_Dish_steak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卷心菜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡腿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GO_Dish_lettuce</t>
+  </si>
+  <si>
+    <t>GO_Dish_ham</t>
+  </si>
+  <si>
+    <t>GO_Dish_tomato</t>
+  </si>
+  <si>
+    <t>GO_Dish_fish</t>
+  </si>
+  <si>
+    <t>GO_Dish_Grilled_Fish</t>
+  </si>
+  <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>土豆咖喱牛腩</t>
+  </si>
+  <si>
+    <t>葱鸡腿</t>
+  </si>
+  <si>
+    <t>GO_Dish_Potato_curry_beef_brisket</t>
+  </si>
+  <si>
+    <t>GO_Dish_Scallion_Chicken_Drumsticks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +184,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -158,10 +224,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -437,14 +503,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="2" max="2" width="24.06640625" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="4" max="4" width="33.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,7 +528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2</v>
       </c>
@@ -475,10 +542,10 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>3</v>
       </c>
@@ -495,7 +562,7 @@
         <v>8001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>4</v>
       </c>
@@ -512,11 +579,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5">
         <v>101</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
@@ -529,11 +596,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6">
         <v>102</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
@@ -546,11 +613,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7">
         <v>201</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
@@ -563,11 +630,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8">
         <v>202</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
@@ -580,11 +647,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9">
         <v>203</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
@@ -597,7 +664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1001</v>
       </c>
@@ -614,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1002</v>
       </c>
@@ -631,7 +698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1003</v>
       </c>
@@ -645,6 +712,159 @@
         <v>29</v>
       </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>103</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>104</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>105</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>106</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>107</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>108</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>204</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>205</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>206</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unity\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF30D39-0C0D-474D-9CA0-C20762EAD487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DB868A-4188-4E3C-AC6A-170E26B6A6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -161,13 +161,14 @@
     <t>土豆咖喱牛腩</t>
   </si>
   <si>
+    <t>GO_Dish_Potato_curry_beef_brisket</t>
+  </si>
+  <si>
+    <t>GO_Dish_Scallion_Chicken_Drumsticks</t>
+  </si>
+  <si>
     <t>葱鸡腿</t>
-  </si>
-  <si>
-    <t>GO_Dish_Potato_curry_beef_brisket</t>
-  </si>
-  <si>
-    <t>GO_Dish_Scallion_Chicken_Drumsticks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -845,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -856,13 +857,13 @@
         <v>206</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21">
         <v>0</v>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unity\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DB868A-4188-4E3C-AC6A-170E26B6A6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723678E3-6ABA-47AB-8C6B-138B426BB3CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="19400" windowHeight="11480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameCharacters" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
   <si>
     <t>ObjectID</t>
   </si>
@@ -112,62 +112,92 @@
     <t>CC_Enemy_03</t>
   </si>
   <si>
+    <t>GO_Dish_lettuce</t>
+  </si>
+  <si>
+    <t>GO_Dish_ham</t>
+  </si>
+  <si>
+    <t>GO_Dish_tomato</t>
+  </si>
+  <si>
+    <t>GO_Dish_fish</t>
+  </si>
+  <si>
+    <t>GO_Dish_Grilled_Fish</t>
+  </si>
+  <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>土豆咖喱牛腩</t>
+  </si>
+  <si>
+    <t>GO_Dish_Potato_curry_beef_brisket</t>
+  </si>
+  <si>
+    <t>GO_Dish_Scallion_Chicken_Drumsticks</t>
+  </si>
+  <si>
+    <t>减速子弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12001|12004</t>
+  </si>
+  <si>
+    <t>牛肉</t>
+  </si>
+  <si>
     <t>GO_Dish_steak</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛肉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>卷心菜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>鸡腿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>土豆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>番茄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GO_Dish_lettuce</t>
-  </si>
-  <si>
-    <t>GO_Dish_ham</t>
-  </si>
-  <si>
-    <t>GO_Dish_tomato</t>
-  </si>
-  <si>
-    <t>GO_Dish_fish</t>
-  </si>
-  <si>
-    <t>GO_Dish_Grilled_Fish</t>
-  </si>
-  <si>
-    <t>烤鱼</t>
-  </si>
-  <si>
-    <t>土豆咖喱牛腩</t>
-  </si>
-  <si>
-    <t>GO_Dish_Potato_curry_beef_brisket</t>
-  </si>
-  <si>
-    <t>GO_Dish_Scallion_Chicken_Drumsticks</t>
   </si>
   <si>
     <t>葱鸡腿</t>
+  </si>
+  <si>
+    <t>散射防御塔</t>
+  </si>
+  <si>
+    <t>CC_Object_Tower_Scatter</t>
+  </si>
+  <si>
+    <t>12002|12004</t>
+  </si>
+  <si>
+    <t>减速防御塔</t>
+  </si>
+  <si>
+    <t>CC_Object_Tower_Slow</t>
+  </si>
+  <si>
+    <t>散射子弹</t>
+  </si>
+  <si>
+    <t>CC_Bullet_Scatter</t>
+  </si>
+  <si>
+    <t>减速子弹</t>
+  </si>
+  <si>
+    <t>CC_Bullet_Slow</t>
+  </si>
+  <si>
+    <t>8003|14002</t>
+  </si>
+  <si>
+    <t>12003|12004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -221,11 +251,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -504,15 +533,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.06640625" customWidth="1"/>
+    <col min="2" max="2" width="24.08203125" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="33.796875" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="5" max="5" width="34.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,162 +559,162 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>16002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E2">
-        <v>12001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3">
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E3">
-        <v>8001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4">
+      <c r="E4">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>101</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>102</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>201</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>202</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>203</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10">
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>1001</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>1002</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
@@ -693,15 +723,15 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
@@ -710,168 +740,253 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1003</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>103</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
         <v>31</v>
       </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>104</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>205</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" t="s">
         <v>37</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>105</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>206</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" t="s">
         <v>38</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>106</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>107</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>108</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>204</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>205</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>206</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723678E3-6ABA-47AB-8C6B-138B426BB3CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECB2F68-D90F-47B4-B1F0-D7F61AA8B99E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-100" yWindow="-100" windowWidth="19400" windowHeight="11480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECB2F68-D90F-47B4-B1F0-D7F61AA8B99E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="19400" windowHeight="11480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="GameCharacters" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>ObjectID</t>
   </si>
@@ -37,6 +44,72 @@
     <t>InitModifier</t>
   </si>
   <si>
+    <t>减速子弹</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+  </si>
+  <si>
+    <t>CC_Bullet_1</t>
+  </si>
+  <si>
+    <t>基础防御塔</t>
+  </si>
+  <si>
+    <t>Tower</t>
+  </si>
+  <si>
+    <t>CC_Object_Tower</t>
+  </si>
+  <si>
+    <t>12001|12004</t>
+  </si>
+  <si>
+    <t>基础子弹</t>
+  </si>
+  <si>
+    <t>空Character作为SpawenRoot</t>
+  </si>
+  <si>
+    <t>SpawnRoot</t>
+  </si>
+  <si>
+    <t>GO_SpawnRoot_1</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>Dish</t>
+  </si>
+  <si>
+    <t>GO_Dish_Potato</t>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+  </si>
+  <si>
+    <t>GO_Dish_Egg</t>
+  </si>
+  <si>
+    <t>炒番茄</t>
+  </si>
+  <si>
+    <t>GO_Dish_Dish1</t>
+  </si>
+  <si>
+    <t>炒鸡蛋</t>
+  </si>
+  <si>
+    <t>GO_Dish_Dish2</t>
+  </si>
+  <si>
+    <t>番茄炒蛋</t>
+  </si>
+  <si>
+    <t>GO_Dish_Dish3</t>
+  </si>
+  <si>
     <t>基础敌人</t>
   </si>
   <si>
@@ -46,127 +119,60 @@
     <t>CC_Enemy_01</t>
   </si>
   <si>
-    <t>基础防御塔</t>
-  </si>
-  <si>
-    <t>Tower</t>
-  </si>
-  <si>
-    <t>CC_Object_Tower</t>
-  </si>
-  <si>
-    <t>基础子弹</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-  </si>
-  <si>
-    <t>CC_Bullet_1</t>
-  </si>
-  <si>
-    <t>空Character作为SpawenRoot</t>
-  </si>
-  <si>
-    <t>SpawnRoot</t>
-  </si>
-  <si>
-    <t>GO_SpawnRoot_1</t>
-  </si>
-  <si>
-    <t>番茄</t>
-  </si>
-  <si>
-    <t>Dish</t>
-  </si>
-  <si>
-    <t>GO_Dish_Potato</t>
-  </si>
-  <si>
-    <t>鸡蛋</t>
-  </si>
-  <si>
-    <t>GO_Dish_Egg</t>
-  </si>
-  <si>
-    <t>炒番茄</t>
-  </si>
-  <si>
-    <t>GO_Dish_Dish1</t>
-  </si>
-  <si>
-    <t>炒鸡蛋</t>
-  </si>
-  <si>
-    <t>GO_Dish_Dish2</t>
-  </si>
-  <si>
-    <t>番茄炒蛋</t>
-  </si>
-  <si>
-    <t>GO_Dish_Dish3</t>
-  </si>
-  <si>
     <t>CC_Enemy_02</t>
   </si>
   <si>
     <t>CC_Enemy_03</t>
   </si>
   <si>
+    <t>牛肉</t>
+  </si>
+  <si>
+    <t>GO_Dish_steak</t>
+  </si>
+  <si>
+    <t>卷心菜</t>
+  </si>
+  <si>
     <t>GO_Dish_lettuce</t>
   </si>
   <si>
+    <t>鸡腿</t>
+  </si>
+  <si>
     <t>GO_Dish_ham</t>
   </si>
   <si>
+    <t>土豆</t>
+  </si>
+  <si>
     <t>GO_Dish_tomato</t>
   </si>
   <si>
+    <t>鱼</t>
+  </si>
+  <si>
     <t>GO_Dish_fish</t>
   </si>
   <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
     <t>GO_Dish_Grilled_Fish</t>
   </si>
   <si>
-    <t>烤鱼</t>
-  </si>
-  <si>
     <t>土豆咖喱牛腩</t>
   </si>
   <si>
     <t>GO_Dish_Potato_curry_beef_brisket</t>
   </si>
   <si>
+    <t>葱鸡腿</t>
+  </si>
+  <si>
     <t>GO_Dish_Scallion_Chicken_Drumsticks</t>
   </si>
   <si>
-    <t>减速子弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12001|12004</t>
-  </si>
-  <si>
-    <t>牛肉</t>
-  </si>
-  <si>
-    <t>GO_Dish_steak</t>
-  </si>
-  <si>
-    <t>卷心菜</t>
-  </si>
-  <si>
-    <t>鸡腿</t>
-  </si>
-  <si>
-    <t>土豆</t>
-  </si>
-  <si>
-    <t>鱼</t>
-  </si>
-  <si>
-    <t>葱鸡腿</t>
-  </si>
-  <si>
     <t>散射防御塔</t>
   </si>
   <si>
@@ -182,30 +188,41 @@
     <t>CC_Object_Tower_Slow</t>
   </si>
   <si>
+    <t>12003|12004</t>
+  </si>
+  <si>
     <t>散射子弹</t>
   </si>
   <si>
     <t>CC_Bullet_Scatter</t>
   </si>
   <si>
-    <t>减速子弹</t>
-  </si>
-  <si>
     <t>CC_Bullet_Slow</t>
   </si>
   <si>
     <t>8003|14002</t>
   </si>
   <si>
-    <t>12003|12004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>AI队友</t>
+  </si>
+  <si>
+    <t>TeamMate</t>
+  </si>
+  <si>
+    <t>CC_AI_TeamMate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,30 +231,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -245,9 +584,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -255,21 +836,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -527,22 +1152,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="24.08203125" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="33.8333333333333" customWidth="1"/>
     <col min="5" max="5" width="34.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -559,24 +1184,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>16002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -590,333 +1215,333 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>8002</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>101</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>102</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>201</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
       <c r="E8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>202</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
       <c r="E9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>203</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
       <c r="E10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1001</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1002</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1003</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>105</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" t="s">
-        <v>19</v>
-      </c>
       <c r="E17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>107</v>
       </c>
       <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
-        <v>18</v>
-      </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>204</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>205</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>206</v>
       </c>
       <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
         <v>47</v>
       </c>
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" t="s">
-        <v>38</v>
-      </c>
       <c r="E22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>10</v>
       </c>
@@ -933,7 +1558,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>11</v>
       </c>
@@ -947,35 +1572,35 @@
         <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E25">
         <v>8002</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
         <v>56</v>
@@ -984,9 +1609,26 @@
         <v>57</v>
       </c>
     </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>2001</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\minigame\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECB2F68-D90F-47B4-B1F0-D7F61AA8B99E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E2B93E-6CCE-42A0-92AF-79AC7D4FC2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="19400" windowHeight="11480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameCharacters" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
   <si>
     <t>ObjectID</t>
   </si>
@@ -198,6 +198,10 @@
   </si>
   <si>
     <t>12003|12004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>满汉全席</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -205,17 +209,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -223,10 +227,17 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,11 +262,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -533,16 +547,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="24.08203125" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
-    <col min="5" max="5" width="34.25" customWidth="1"/>
+    <col min="2" max="2" width="24.09765625" customWidth="1"/>
+    <col min="3" max="3" width="15.296875" customWidth="1"/>
+    <col min="4" max="4" width="33.796875" customWidth="1"/>
+    <col min="5" max="5" width="34.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -559,7 +573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>5</v>
       </c>
@@ -576,7 +590,7 @@
         <v>16002</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -593,7 +607,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -610,7 +624,7 @@
         <v>8002</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -627,7 +641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>101</v>
       </c>
@@ -644,7 +658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>102</v>
       </c>
@@ -661,7 +675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>201</v>
       </c>
@@ -678,7 +692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>202</v>
       </c>
@@ -695,7 +709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>203</v>
       </c>
@@ -712,7 +726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1001</v>
       </c>
@@ -729,7 +743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1002</v>
       </c>
@@ -746,7 +760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1003</v>
       </c>
@@ -763,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>103</v>
       </c>
@@ -780,7 +794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>104</v>
       </c>
@@ -797,7 +811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>105</v>
       </c>
@@ -814,7 +828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>106</v>
       </c>
@@ -831,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>107</v>
       </c>
@@ -848,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>108</v>
       </c>
@@ -865,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>204</v>
       </c>
@@ -882,7 +896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>205</v>
       </c>
@@ -899,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>206</v>
       </c>
@@ -916,71 +930,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23">
+        <v>207</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>10</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>48</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>11</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="26" spans="1:5">
+      <c r="A26">
         <v>20</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>53</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25">
-        <v>8002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>21</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="D26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
         <v>56</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E27" t="s">
         <v>57</v>
       </c>
     </row>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\FoodGuardian\Project3D\Assets\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E2B93E-6CCE-42A0-92AF-79AC7D4FC2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8292D1B2-6033-4CD8-ACFE-8AC806A9D842}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameCharacters" sheetId="1" r:id="rId1"/>
@@ -139,59 +139,52 @@
     <t>GO_Dish_Scallion_Chicken_Drumsticks</t>
   </si>
   <si>
+    <t>12001|12004</t>
+  </si>
+  <si>
+    <t>牛肉</t>
+  </si>
+  <si>
+    <t>GO_Dish_steak</t>
+  </si>
+  <si>
+    <t>卷心菜</t>
+  </si>
+  <si>
+    <t>鸡腿</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>鱼</t>
+  </si>
+  <si>
+    <t>葱鸡腿</t>
+  </si>
+  <si>
+    <t>散射防御塔</t>
+  </si>
+  <si>
+    <t>CC_Object_Tower_Scatter</t>
+  </si>
+  <si>
+    <t>12002|12004</t>
+  </si>
+  <si>
+    <t>减速防御塔</t>
+  </si>
+  <si>
+    <t>CC_Object_Tower_Slow</t>
+  </si>
+  <si>
+    <t>散射子弹</t>
+  </si>
+  <si>
+    <t>CC_Bullet_Scatter</t>
+  </si>
+  <si>
     <t>减速子弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12001|12004</t>
-  </si>
-  <si>
-    <t>牛肉</t>
-  </si>
-  <si>
-    <t>GO_Dish_steak</t>
-  </si>
-  <si>
-    <t>卷心菜</t>
-  </si>
-  <si>
-    <t>鸡腿</t>
-  </si>
-  <si>
-    <t>土豆</t>
-  </si>
-  <si>
-    <t>鱼</t>
-  </si>
-  <si>
-    <t>葱鸡腿</t>
-  </si>
-  <si>
-    <t>散射防御塔</t>
-  </si>
-  <si>
-    <t>CC_Object_Tower_Scatter</t>
-  </si>
-  <si>
-    <t>12002|12004</t>
-  </si>
-  <si>
-    <t>减速防御塔</t>
-  </si>
-  <si>
-    <t>CC_Object_Tower_Slow</t>
-  </si>
-  <si>
-    <t>散射子弹</t>
-  </si>
-  <si>
-    <t>CC_Bullet_Scatter</t>
-  </si>
-  <si>
-    <t>减速子弹</t>
-  </si>
-  <si>
-    <t>CC_Bullet_Slow</t>
   </si>
   <si>
     <t>8003|14002</t>
@@ -202,6 +195,13 @@
   </si>
   <si>
     <t>满汉全席</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle_item_MC21</t>
+  </si>
+  <si>
+    <t>普通子弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -213,13 +213,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -227,7 +227,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -548,12 +548,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="24.09765625" customWidth="1"/>
-    <col min="3" max="3" width="15.296875" customWidth="1"/>
-    <col min="4" max="4" width="33.796875" customWidth="1"/>
-    <col min="5" max="5" width="34.19921875" customWidth="1"/>
+    <col min="2" max="2" width="24.08203125" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="5" max="5" width="34.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -578,13 +578,13 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
+      <c r="D2" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E2">
         <v>16002</v>
@@ -604,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -782,13 +782,13 @@
         <v>103</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -816,7 +816,7 @@
         <v>105</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -833,7 +833,7 @@
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -867,7 +867,7 @@
         <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -918,7 +918,7 @@
         <v>206</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
@@ -935,7 +935,7 @@
         <v>207</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
@@ -949,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" t="s">
         <v>49</v>
-      </c>
-      <c r="E24" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -966,16 +966,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -983,13 +983,13 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E26">
         <v>8002</v>
@@ -1000,16 +1000,16 @@
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
-      <c r="D27" t="s">
-        <v>56</v>
+      <c r="D27" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8292D1B2-6033-4CD8-ACFE-8AC806A9D842}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE1D114-F20B-4AA1-9FF0-EFBD590CF82B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
   <si>
     <t>ObjectID</t>
   </si>
@@ -202,6 +202,10 @@
   </si>
   <si>
     <t>普通子弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle_item_MC11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -584,7 +588,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2">
         <v>16002</v>

--- a/Assets/Configs/GameCharacters.xlsx
+++ b/Assets/Configs/GameCharacters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project3D\Assets\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE1D114-F20B-4AA1-9FF0-EFBD590CF82B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AA1930-D76F-49DE-B3C2-5ED2B23107C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="59">
   <si>
     <t>ObjectID</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Bullet</t>
   </si>
   <si>
-    <t>CC_Bullet_1</t>
-  </si>
-  <si>
     <t>空Character作为SpawenRoot</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
   </si>
   <si>
     <t>散射子弹</t>
-  </si>
-  <si>
-    <t>CC_Bullet_Scatter</t>
   </si>
   <si>
     <t>减速子弹</t>
@@ -582,13 +576,13 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2">
         <v>16002</v>
@@ -608,7 +602,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -621,8 +615,8 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
+      <c r="D4" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E4">
         <v>8002</v>
@@ -633,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -650,13 +644,13 @@
         <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -667,13 +661,13 @@
         <v>102</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -684,13 +678,13 @@
         <v>201</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -701,13 +695,13 @@
         <v>202</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -718,13 +712,13 @@
         <v>203</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -758,7 +752,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -775,7 +769,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -786,13 +780,13 @@
         <v>103</v>
       </c>
       <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -803,13 +797,13 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -820,13 +814,13 @@
         <v>105</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -837,13 +831,13 @@
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
         <v>18</v>
-      </c>
-      <c r="D17" t="s">
-        <v>19</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -854,13 +848,13 @@
         <v>107</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -871,13 +865,13 @@
         <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -888,13 +882,13 @@
         <v>204</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -905,13 +899,13 @@
         <v>205</v>
       </c>
       <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
         <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" t="s">
-        <v>37</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -922,13 +916,13 @@
         <v>206</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -939,10 +933,10 @@
         <v>207</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -953,16 +947,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" t="s">
         <v>48</v>
-      </c>
-      <c r="E24" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -970,16 +964,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -987,13 +981,13 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
-      <c r="D26" t="s">
-        <v>53</v>
+      <c r="D26" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E26">
         <v>8002</v>
@@ -1004,16 +998,16 @@
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
